--- a/backend/Expense_details.xlsx
+++ b/backend/Expense_details.xlsx
@@ -412,32 +412,32 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Food (sushi)</v>
+        <v>sushi food</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C2" t="str">
-        <v>Sat Dec 20 2025 01:00:00 GM</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>investing in crypto</v>
+        <v>loss in investement</v>
       </c>
       <c r="B3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="C3" t="str">
-        <v>Sat Dec 20 2025 01:00:00 GM</v>
+        <v>Wed Dec 24 2025 01:00:00 GM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Rent</v>
+        <v>diesel</v>
       </c>
       <c r="B4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -445,13 +445,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Food</v>
+        <v>new setup</v>
       </c>
       <c r="B5">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="C5" t="str">
-        <v>Mon Dec 08 2025 01:00:00 GM</v>
+        <v/>
       </c>
     </row>
   </sheetData>
